--- a/01-foundations/04-basic-formulas/1.4-basic-formulas.xlsx
+++ b/01-foundations/04-basic-formulas/1.4-basic-formulas.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -295,32 +295,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -873,7 +870,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1">
+    <row r="16" ht="18" customHeight="1">
       <c r="B16" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -881,7 +878,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -937,7 +934,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -961,7 +958,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -981,7 +978,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Data: 90 rows — Excel Table 'tblCensus'</t>
+          <t>Data: 90 rows, in the Excel Table 'tblCensus'</t>
         </is>
       </c>
     </row>
@@ -993,7 +990,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 14 rows — Excel Table 'tblSupplies'</t>
+          <t>Data: 14 rows, in the Excel Table 'tblSupplies'</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3855,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3872,7 +3869,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="35" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3924,7 @@
           <t>=SUM(Census!C2:C91)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="39">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">SUM(Census!C2:C91)</f>
         <v/>
       </c>
@@ -3948,7 +3945,7 @@
           <t>What was the average midnight census? (Keep full precision — the check accepts 2 decimal places.)</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n">
+      <c r="C6" s="39" t="n">
         <v>32.85555555555555</v>
       </c>
       <c r="D6" s="38" t="inlineStr">
@@ -3956,13 +3953,13 @@
           <t>=AVERAGE(Census!E2:E91)</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="41">
+      <c r="E6" cm="1" s="40">
         <f t="array" ref="E6">AVERAGE(Census!E2:E91)</f>
         <v/>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>AVERAGE = SUM ÷ COUNT of the numbers in the range. This is the unit's *average daily census* (ADC).</t>
+          <t>AVERAGE = SUM ÷ COUNT of the numbers in the range. This is the unit's average daily census (ADC).</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3982,7 @@
           <t>=MAX(Census!E2:E91)</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="39">
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">MAX(Census!E2:E91)</f>
         <v/>
       </c>
@@ -4010,7 +4007,7 @@
           <t>=MIN(Census!E2:E91)</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="39">
+      <c r="E8" cm="1" s="19">
         <f t="array" ref="E8">MIN(Census!E2:E91)</f>
         <v/>
       </c>
@@ -4035,7 +4032,7 @@
           <t>=COUNT(Census!A2:A91)</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="39">
+      <c r="E9" cm="1" s="19">
         <f t="array" ref="E9">COUNT(Census!A2:A91)</f>
         <v/>
       </c>
@@ -4064,7 +4061,7 @@
           <t>=COUNTA(Census!F2:F91)</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="39">
+      <c r="E10" cm="1" s="19">
         <f t="array" ref="E10">COUNTA(Census!F2:F91)</f>
         <v/>
       </c>
@@ -4093,7 +4090,7 @@
           <t>=COUNTBLANK(Census!F2:F91)</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="39">
+      <c r="E11" cm="1" s="19">
         <f t="array" ref="E11">COUNTBLANK(Census!F2:F91)</f>
         <v/>
       </c>
@@ -4122,7 +4119,7 @@
           <t>=SUM(Census!E2:E91)</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="39">
+      <c r="E12" cm="1" s="19">
         <f t="array" ref="E12">SUM(Census!E2:E91)</f>
         <v/>
       </c>
@@ -4143,7 +4140,7 @@
           <t>What was the unit's occupancy rate for the whole quarter? Divide total patient days by total staffed-bed days. Enter it as a percentage.</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n">
+      <c r="C13" s="41" t="n">
         <v>0.9126543209876543</v>
       </c>
       <c r="D13" s="38" t="inlineStr">
@@ -4151,7 +4148,7 @@
           <t>=SUM(Census!E2:E91)/SUM(Census!B2:B91)</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="43">
+      <c r="E13" cm="1" s="42">
         <f t="array" ref="E13">SUM(Census!E2:E91)/SUM(Census!B2:B91)</f>
         <v/>
       </c>
@@ -4180,7 +4177,7 @@
           <t>=E2/B2</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="39">
+      <c r="E14" cm="1" s="19">
         <f t="array" ref="E14">SUMPRODUCT(--(Census!E2:E91&gt;=Census!B2:B91))</f>
         <v/>
       </c>
@@ -4201,7 +4198,7 @@
           <t>Average length of stay (ALOS) = patient days ÷ discharges. Calculate it for the quarter, rounded to 1 decimal place with ROUND.</t>
         </is>
       </c>
-      <c r="C15" s="44" t="n">
+      <c r="C15" s="43" t="n">
         <v>4.2</v>
       </c>
       <c r="D15" s="38" t="inlineStr">
@@ -4209,7 +4206,7 @@
           <t>=ROUND(SUM(Census!E2:E91)/SUM(Census!D2:D91),1)</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="45">
+      <c r="E15" cm="1" s="44">
         <f t="array" ref="E15">ROUND(SUM(Census!E2:E91)/SUM(Census!D2:D91),1)</f>
         <v/>
       </c>
@@ -4238,7 +4235,7 @@
           <t>=(30-6)/4+2^3</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="39">
+      <c r="E16" cm="1" s="19">
         <f t="array" ref="E16">(30-6)/4+2^3</f>
         <v/>
       </c>
@@ -4259,7 +4256,7 @@
           <t>Switch to the Supplies sheet. Fill the yellow StockValue column with UnitCost × QtyOnHand for every item. The gray cell totals your column — what is the total value of 4 West's supply room?</t>
         </is>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C17" s="45" t="n">
         <v>31730.68</v>
       </c>
       <c r="D17" s="38" t="inlineStr">
@@ -4267,7 +4264,7 @@
           <t>=E2*F2</t>
         </is>
       </c>
-      <c r="E17" cm="1" s="47">
+      <c r="E17" cm="1" s="46">
         <f t="array" ref="E17">SUMPRODUCT(Supplies!E2:E15,Supplies!F2:F15)</f>
         <v/>
       </c>
@@ -4300,7 +4297,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4314,7 +4311,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="35" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4358,7 @@
           <t>What was February's average daily census (ADC)? Use only the February rows.</t>
         </is>
       </c>
-      <c r="C5" s="40" t="n">
+      <c r="C5" s="39" t="n">
         <v>32.82142857142857</v>
       </c>
       <c r="D5" s="38" t="inlineStr">
@@ -4369,7 +4366,7 @@
           <t>=AVERAGE(Census!E33:E60)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="41">
+      <c r="E5" cm="1" s="40">
         <f t="array" ref="E5">AVERAGE(Census!E33:E60)</f>
         <v/>
       </c>
@@ -4390,7 +4387,7 @@
           <t>How many beds would 4 West have needed in February for that ADC to equal 85% occupancy? (ADC ÷ 0.85, keep the decimals.)</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n">
+      <c r="C6" s="39" t="n">
         <v>38.61344537815126</v>
       </c>
       <c r="D6" s="38" t="inlineStr">
@@ -4398,7 +4395,7 @@
           <t>=AVERAGE(Census!E33:E60)/0.85</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="41">
+      <c r="E6" cm="1" s="40">
         <f t="array" ref="E6">AVERAGE(Census!E33:E60)/0.85</f>
         <v/>
       </c>
@@ -4423,7 +4420,7 @@
           <t>=ROUNDUP(AVERAGE(Census!E33:E60)/0.85-Census!B33,0)</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="39">
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">ROUNDUP(AVERAGE(Census!E33:E60)/0.85-Census!B33,0)</f>
         <v/>
       </c>
@@ -4452,7 +4449,7 @@
           <t>=COUNTIF(Census!E33:E60,"&gt;"&amp;0.85*36)</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="39">
+      <c r="E8" cm="1" s="19">
         <f t="array" ref="E8">COUNTIF(Census!E33:E60,"&gt;"&amp;0.85*36)</f>
         <v/>
       </c>

--- a/01-foundations/04-basic-formulas/1.4-basic-formulas.xlsx
+++ b/01-foundations/04-basic-formulas/1.4-basic-formulas.xlsx
@@ -741,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C30"/>
+  <dimension ref="B2:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Beginner  ·  about 45 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Beginner  ·  about 55 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -973,46 +973,70 @@
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Census</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Data: 90 rows, in the Excel Table 'tblCensus'</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
         <is>
+          <t>Census</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Data: 90 rows, in the Excel Table 'tblCensus'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>Supplies</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Data: 14 rows, in the Excel Table 'tblSupplies'</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="33" customHeight="1">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Daily census for Medical-Surgical 4 West at Bluestone Memorial Hospital, Jan–Mar 2025 (90 days), plus the unit's supply room stock.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (4 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33" customHeight="1">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Daily census for Medical-Surgical 4 West at Bluestone Memorial Hospital, Jan–Mar 2025 (90 days), plus the unit's supply room stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -4154,7 +4178,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>A rate for a whole period should be total numerator ÷ total denominator. Format the cell as a percentage (Ctrl+Shift+%) to see 91.3% instead of 0.9126…</t>
+          <t>A rate for a whole period should be total numerator ÷ total denominator. Format the cell as a percentage (Ctrl + Shift + %, Mac: ⌃ + Shift + %) to see 91.3% instead of 0.9126…</t>
         </is>
       </c>
     </row>

--- a/01-foundations/04-basic-formulas/1.4-basic-formulas.xlsx
+++ b/01-foundations/04-basic-formulas/1.4-basic-formulas.xlsx
@@ -858,7 +858,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -866,7 +866,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell. For tasks 10 and 13, fill the yellow column on the Census or Supplies sheet instead, and the task's gray cell on Practice reads it.</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>All tasks use the Census sheet (4 West, Q1 2025) unless they say otherwise. Use cell ranges like Census!C2:C91 — or click and drag to select them while typing a formula.</t>
+          <t>All tasks use the Census sheet (4 West, Q1 2025) unless they say otherwise. Use cell ranges like Census!C2:C91, or click and drag to select them while typing a formula.</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>What was the average midnight census? (Keep full precision — the check accepts 2 decimal places.)</t>
+          <t>What was the average midnight census? (Keep full precision. The check compares the value to 2 decimal places.)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>COUNT counts numbers — and dates are numbers</t>
+          <t>COUNT counts numbers, and dates are numbers</t>
         </is>
       </c>
       <c r="D10" s="21" t="n"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Switch to the Supplies sheet. Fill the yellow StockValue column with UnitCost × QtyOnHand for every item. The gray cell totals your column — what is the total value of 4 West's supply room?</t>
+          <t>Switch to the Supplies sheet. Fill the yellow StockValue column with UnitCost × QtyOnHand for every item. The gray cell totals your column. What is the total value of 4 West's supply room?</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -3714,7 +3714,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>The Chief Nursing Officer says February felt 'impossibly full' on 4 West and asks whether the unit needs more staffed beds. Hospitals often plan beds so average occupancy is about 85% — enough slack to absorb surges. February is rows 33–60 of the Census sheet.</t>
+          <t>The Chief Nursing Officer says February felt 'impossibly full' on 4 West and asks whether the unit needs more staffed beds. Hospitals often plan beds so average occupancy is about 85%, which leaves enough slack to absorb surges. February is rows 33–60 of the Census sheet.</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>COUNTIF(range, "&gt;30.6") — a preview of Lesson 2.5</t>
+          <t>COUNTIF(range, "&gt;30.6"), a preview of Lesson 2.5</t>
         </is>
       </c>
       <c r="D9" s="21" t="n"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>What was the average midnight census? (Keep full precision — the check accepts 2 decimal places.)</t>
+          <t>What was the average midnight census? (Keep full precision. The check compares the value to 2 decimal places.)</t>
         </is>
       </c>
       <c r="C6" s="39" t="n">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="66" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>A rate for a whole period should be total numerator ÷ total denominator. Format the cell as a percentage (Ctrl + Shift + %, Mac: ⌃ + Shift + %) to see 91.3% instead of 0.9126…</t>
+          <t>A rate for a whole period should be total numerator ÷ total denominator. Format the cell as a percentage (Ctrl + Shift + %, Mac: Control + Shift + %) to see 91.3% instead of 0.9126…</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Type =E2/B2 in the first Occupancy cell and copy it down; each row's formula points to its own row (=E3/B3, =E4/B4 …). Because the data is an Excel Table, typing the formula in one cell may fill the whole column automatically — and you may see it written as =[@MidnightCensus]/[@StaffedBeds]. Both are correct.</t>
+          <t>Type =E2/B2 in the first Occupancy cell and copy it down. Each row's formula points to its own row (=E3/B3, =E4/B4 …). Because the data is an Excel Table, typing the formula in one cell may fill the whole column automatically, and you may see it written as =[@MidnightCensus]/[@StaffedBeds]. Both are correct.</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Switch to the Supplies sheet. Fill the yellow StockValue column with UnitCost × QtyOnHand for every item. The gray cell totals your column — what is the total value of 4 West's supply room?</t>
+          <t>Switch to the Supplies sheet. Fill the yellow StockValue column with UnitCost × QtyOnHand for every item. The gray cell totals your column. What is the total value of 4 West's supply room?</t>
         </is>
       </c>
       <c r="C17" s="45" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>One formula, copied down, gives each item's value; then SUM the column. (The live formula in the key uses SUMPRODUCT, which multiplies and adds in one step — you'll meet it in Lesson 2.4.)</t>
+          <t>One formula, copied down, gives each item's value, and then SUM adds up the column. (The live formula in the key uses SUMPRODUCT, which multiplies and adds in one step. You'll meet it in Lesson 2.4.)</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>COUNTIF counts cells that meet a condition. You'll master it in Lesson 2.5 — here it confirms that almost every February day ran above the 85% planning target.</t>
+          <t>COUNTIF counts cells that meet a condition, and you'll master it in Lesson 2.5. Here it confirms that almost every February day ran above the 85% planning target.</t>
         </is>
       </c>
     </row>
